--- a/data/weekly_menu.xlsx
+++ b/data/weekly_menu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KICE\Desktop\바이브 코딩\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KICE\Desktop\바이브 코딩\메뉴 배포용 앱 폴더_26.8.12\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC4A6FC-8A6F-4F00-A5DA-A2BCCF6CFCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BC92797-6C53-4B85-9918-2E10AA259B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간식단표" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="57">
   <si>
     <t>주간식단표</t>
   </si>
@@ -34,19 +34,55 @@
     <t>(주) 한울F&amp;S · 한국교육과정평가원</t>
   </si>
   <si>
-    <t>08월 10일</t>
-  </si>
-  <si>
-    <t>08월 11일</t>
-  </si>
-  <si>
-    <t>08월 12일</t>
-  </si>
-  <si>
-    <t>08월 13일</t>
-  </si>
-  <si>
-    <t>08월 14일</t>
+    <t>중식</t>
+  </si>
+  <si>
+    <t>MENU</t>
+  </si>
+  <si>
+    <t>PLUS BAR</t>
+  </si>
+  <si>
+    <t>석식</t>
+  </si>
+  <si>
+    <t>식사시간  중식 11:30-12:30 / 석식 17:30-18:30</t>
+  </si>
+  <si>
+    <t>상기 식단은 식자재 수급사정에 의해 변경될 수 있습니다. 원산지 표시는 일일 메뉴표에 별도 표기됩니다.</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>요일</t>
+  </si>
+  <si>
+    <t>식사구분</t>
+  </si>
+  <si>
+    <t>메뉴순번</t>
+  </si>
+  <si>
+    <t>메뉴명</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>08월 17일</t>
+  </si>
+  <si>
+    <t>08월 18일</t>
+  </si>
+  <si>
+    <t>08월 19일</t>
+  </si>
+  <si>
+    <t>08월 20일</t>
+  </si>
+  <si>
+    <t>08월 21일</t>
   </si>
   <si>
     <t>월</t>
@@ -64,193 +100,103 @@
     <t>금</t>
   </si>
   <si>
-    <t>중식</t>
-  </si>
-  <si>
-    <t>MENU</t>
-  </si>
-  <si>
-    <t>마파두부가지덮밥</t>
-  </si>
-  <si>
-    <t>육개장</t>
-  </si>
-  <si>
-    <t>돈육콩나물볶음</t>
-  </si>
-  <si>
-    <t>짜장면</t>
-  </si>
-  <si>
-    <t>[말복]닭곰탕&amp;소면사리</t>
+    <t>광복절 대체공휴일</t>
+  </si>
+  <si>
+    <t>보리열무비빔밥&amp;계란후라이</t>
+  </si>
+  <si>
+    <t>멘치까스&amp;소스</t>
+  </si>
+  <si>
+    <t>햄야채볶음밥</t>
+  </si>
+  <si>
+    <t>개원기념일 휴무</t>
+  </si>
+  <si>
+    <t>맑은미역국</t>
+  </si>
+  <si>
+    <t>김치콩나물국</t>
+  </si>
+  <si>
+    <t>숯불비빔라면</t>
+  </si>
+  <si>
+    <t>돈민찌두부조림</t>
+  </si>
+  <si>
+    <t>건파래볶음</t>
+  </si>
+  <si>
+    <t>삼색계란찜</t>
+  </si>
+  <si>
+    <t>쥐어채볶음</t>
+  </si>
+  <si>
+    <t>부추겉절이</t>
   </si>
   <si>
     <t>어묵국</t>
   </si>
   <si>
-    <t>생선까스&amp;타르타르소스</t>
-  </si>
-  <si>
-    <t>배추된장국</t>
-  </si>
-  <si>
-    <t>파계란국</t>
-  </si>
-  <si>
-    <t>순대콩나물찜</t>
-  </si>
-  <si>
-    <t>탕수육&amp;소스</t>
-  </si>
-  <si>
-    <t>매운두부조림</t>
-  </si>
-  <si>
-    <t>사각어묵볶음</t>
-  </si>
-  <si>
-    <t>춘권튀김&amp;칠리소스</t>
-  </si>
-  <si>
-    <t>도토리묵&amp;양념간장</t>
+    <t>들기름묵은지볶음</t>
+  </si>
+  <si>
+    <t>깍두기</t>
+  </si>
+  <si>
+    <t>현미밥</t>
+  </si>
+  <si>
+    <t>쌀밥/현미밥</t>
+  </si>
+  <si>
+    <t>그린샐러드</t>
+  </si>
+  <si>
+    <t>둥글레차</t>
+  </si>
+  <si>
+    <t>눌은밥</t>
+  </si>
+  <si>
+    <t>미숫가루</t>
+  </si>
+  <si>
+    <t>카레라이스</t>
+  </si>
+  <si>
+    <t>우거지해장국</t>
+  </si>
+  <si>
+    <t>유부장국</t>
+  </si>
+  <si>
+    <t>산적구이&amp;크리미어니언소스</t>
+  </si>
+  <si>
+    <t>비엔나떡볶음</t>
+  </si>
+  <si>
+    <t>매운어묵볶음</t>
+  </si>
+  <si>
+    <t>오이피클</t>
   </si>
   <si>
     <t>콩나물무침</t>
   </si>
   <si>
-    <t>들깨무나물</t>
-  </si>
-  <si>
-    <t>무말랭이지</t>
-  </si>
-  <si>
-    <t>단무지</t>
-  </si>
-  <si>
-    <t>마늘쫑무침</t>
-  </si>
-  <si>
     <t>포기김치</t>
   </si>
   <si>
-    <t>들기름묵은지볶음</t>
-  </si>
-  <si>
-    <t>깍두기</t>
-  </si>
-  <si>
-    <t>현미밥</t>
-  </si>
-  <si>
-    <t>쌀밥/현미밥</t>
-  </si>
-  <si>
-    <t>PLUS BAR</t>
-  </si>
-  <si>
-    <t>그린샐러드</t>
-  </si>
-  <si>
-    <t>마카로니샐러드</t>
-  </si>
-  <si>
-    <t>메밀차</t>
-  </si>
-  <si>
-    <t>율무차</t>
-  </si>
-  <si>
-    <t>녹차</t>
-  </si>
-  <si>
-    <t>요구르트</t>
-  </si>
-  <si>
-    <t>수정과</t>
-  </si>
-  <si>
-    <t>석식</t>
-  </si>
-  <si>
-    <t>고등어무조림</t>
-  </si>
-  <si>
-    <t>돈육모둠장조림</t>
-  </si>
-  <si>
-    <t>취나물밥&amp;양념간장</t>
-  </si>
-  <si>
-    <t>우삼겹갈비탕</t>
-  </si>
-  <si>
-    <t>들깨미역국</t>
-  </si>
-  <si>
-    <t>두부김치국</t>
-  </si>
-  <si>
-    <t>고기손만두찜</t>
-  </si>
-  <si>
-    <t>두부강정</t>
-  </si>
-  <si>
-    <t>시래기나물</t>
-  </si>
-  <si>
-    <t>미역줄기볶음</t>
-  </si>
-  <si>
-    <t>팽이맑은국</t>
-  </si>
-  <si>
-    <t>명엽채볶음</t>
-  </si>
-  <si>
-    <t>오복채무침</t>
-  </si>
-  <si>
-    <t>오이부추무침</t>
-  </si>
-  <si>
-    <t>멸치고추장조림</t>
-  </si>
-  <si>
-    <t>양념깻잎지</t>
-  </si>
-  <si>
-    <t>미역초무침</t>
-  </si>
-  <si>
     <t>쌀밥</t>
   </si>
   <si>
-    <t>식사시간  중식 11:30-12:30 / 석식 17:30-18:30</t>
-  </si>
-  <si>
-    <t>상기 식단은 식자재 수급사정에 의해 변경될 수 있습니다. 원산지 표시는 일일 메뉴표에 별도 표기됩니다.</t>
-  </si>
-  <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>요일</t>
-  </si>
-  <si>
-    <t>식사구분</t>
-  </si>
-  <si>
-    <t>메뉴순번</t>
-  </si>
-  <si>
-    <t>메뉴명</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>금요일 석식은 운영하지 않습니다.</t>
+    <t>석식 미운영</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -735,6 +681,45 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -742,45 +727,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1020,210 +966,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="48" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26.1" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A6" s="21"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A7" s="21"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A8" s="21"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A9" s="21"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A11" s="21"/>
+      <c r="B11" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A6" s="28"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A9" s="28"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A12" s="29"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="5" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="22"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
         <v>43</v>
       </c>
@@ -1233,142 +1153,124 @@
       <c r="F12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A13" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="E13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="30" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="3" t="s">
+      <c r="F15" s="4"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F16" s="4"/>
+      <c r="G16" s="24"/>
+    </row>
+    <row r="17" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="E17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="24"/>
+    </row>
+    <row r="18" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="31"/>
-    </row>
-    <row r="15" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="31"/>
-    </row>
-    <row r="16" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="31"/>
-    </row>
-    <row r="17" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="31"/>
-    </row>
-    <row r="18" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="32"/>
+        <v>55</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A19" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="23"/>
+      <c r="A19" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A20" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="26"/>
+      <c r="A20" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="B5:B10"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="G13:G18"/>
@@ -1376,10 +1278,6 @@
     <mergeCell ref="A13:A18"/>
     <mergeCell ref="B13:B18"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="B5:B10"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1401,73 +1299,65 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5">
       <c r="A1" s="6" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="9">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="10">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D2" s="10"/>
       <c r="E2" s="11" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="10">
-        <v>2</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>19</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="9">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="10">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D4" s="10"/>
       <c r="E4" s="11" t="s">
         <v>24</v>
       </c>
@@ -1475,1116 +1365,888 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D5" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D7" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D8" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D9" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D10" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D11" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D12" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F12" s="12"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D13" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D14" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="9">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D15" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="9">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D16" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F16" s="12"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D17" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="9">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D18" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F18" s="12"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D19" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D20" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D21" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F21" s="12"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D22" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="10">
+        <v>5</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="D23" s="10">
-        <v>2</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="F23" s="12"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D24" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F24" s="12"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D25" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F25" s="12"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D26" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C27" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="10">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="D27" s="10">
-        <v>4</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D28" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="9">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D29" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F29" s="12"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D30" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="9">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D31" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="9">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D32" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F32" s="12"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D33" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F33" s="12"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D34" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F34" s="12"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D35" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F35" s="12"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D36" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C37" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="10">
+        <v>5</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="D37" s="10">
-        <v>2</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D38" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D39" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D40" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="9">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="10">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D41" s="10"/>
       <c r="E41" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F41" s="12"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="9">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="10">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D42" s="10"/>
       <c r="E42" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F42" s="12"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="9">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="10">
-        <v>6</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>34</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D43" s="10"/>
+      <c r="E43" s="11"/>
       <c r="F43" s="12"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="9">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="10">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D44" s="10"/>
       <c r="E44" s="11" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F44" s="12"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="10">
-        <v>2</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="11"/>
       <c r="F45" s="12"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="10">
-        <v>3</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>27</v>
-      </c>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="11"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="10">
-        <v>4</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>32</v>
-      </c>
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="11"/>
       <c r="F47" s="12"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" s="10">
-        <v>5</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>34</v>
-      </c>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="11"/>
       <c r="F48" s="12"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="10">
-        <v>6</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="11"/>
       <c r="F49" s="12"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="10">
-        <v>1</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>41</v>
-      </c>
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="11"/>
       <c r="F50" s="12"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="10">
-        <v>2</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>45</v>
-      </c>
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="11"/>
       <c r="F51" s="12"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" s="10">
-        <v>1</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="11"/>
       <c r="F52" s="12"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="10">
-        <v>2</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="11"/>
       <c r="F53" s="12"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" s="10">
-        <v>3</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>59</v>
-      </c>
+      <c r="A54" s="9"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="11"/>
       <c r="F54" s="12"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" s="10">
-        <v>4</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="A55" s="9"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="11"/>
       <c r="F55" s="12"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D56" s="10">
-        <v>5</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>36</v>
-      </c>
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="11"/>
       <c r="F56" s="12"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="9">
-        <v>46247</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="10">
-        <v>6</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>65</v>
-      </c>
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="11"/>
       <c r="F57" s="12"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="10">
-        <v>1</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="A58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="11"/>
       <c r="F58" s="12"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="10">
-        <v>2</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>23</v>
-      </c>
+      <c r="A59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="11"/>
       <c r="F59" s="12"/>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D60" s="10">
-        <v>3</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>28</v>
-      </c>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="11"/>
       <c r="F60" s="12"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D61" s="10">
-        <v>4</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A61" s="9"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="11"/>
       <c r="F61" s="12"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="10">
-        <v>5</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>36</v>
-      </c>
+      <c r="A62" s="9"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="11"/>
       <c r="F62" s="12"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D63" s="10">
-        <v>6</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="A63" s="9"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="11"/>
       <c r="F63" s="12"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="10">
-        <v>1</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="A64" s="9"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="11"/>
       <c r="F64" s="12"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="9">
-        <v>46248</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65" s="10">
-        <v>2</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>46</v>
-      </c>
+      <c r="A65" s="9"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="12"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="13">
-        <v>46248</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>47</v>
-      </c>
+      <c r="A66" s="13"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
       <c r="D66" s="14"/>
-      <c r="E66" s="15" t="s">
-        <v>74</v>
-      </c>
+      <c r="E66" s="15"/>
       <c r="F66" s="16"/>
     </row>
   </sheetData>
